--- a/DLF Applications.xlsx
+++ b/DLF Applications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClaJec0\PycharmProjects\UpdateApplicationAssetsInTOPdesk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3166214-C16A-4651-8993-FFBE745A36EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A607764-EEB6-4527-8695-04041E1D7316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="0" windowWidth="27165" windowHeight="20880" firstSheet="1" activeTab="2" xr2:uid="{5C8198AA-DEA0-DA46-990C-E2DC7E26B2E4}"/>
+    <workbookView xWindow="975" yWindow="360" windowWidth="27165" windowHeight="20880" firstSheet="1" activeTab="2" xr2:uid="{5C8198AA-DEA0-DA46-990C-E2DC7E26B2E4}"/>
   </bookViews>
   <sheets>
     <sheet name="DLF Applications" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,8 @@
     <sheet name="TOPdesk format (no duplicates)" sheetId="11" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="4" hidden="1">'TOPdesk format (no duplicates)'!$A$1:$AE$98</definedName>
-    <definedName name="ExternalData_2" localSheetId="2" hidden="1">'Separated Entries'!$A$1:$E$108</definedName>
+    <definedName name="ExternalData_1" localSheetId="4" hidden="1">'TOPdesk format (no duplicates)'!$A$1:$X$110</definedName>
+    <definedName name="ExternalData_2" localSheetId="2" hidden="1">'Separated Entries'!$A$1:$D$124</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="298">
   <si>
     <t>New table</t>
   </si>
@@ -622,21 +622,12 @@
     <t>specification</t>
   </si>
   <si>
-    <t>application</t>
-  </si>
-  <si>
-    <t>strategic-business-unit-sbu</t>
-  </si>
-  <si>
     <t>country</t>
   </si>
   <si>
     <t>city</t>
   </si>
   <si>
-    <t>address</t>
-  </si>
-  <si>
     <t>brief-description</t>
   </si>
   <si>
@@ -646,18 +637,6 @@
     <t>compliance-status</t>
   </si>
   <si>
-    <t>developed</t>
-  </si>
-  <si>
-    <t>in-prod</t>
-  </si>
-  <si>
-    <t>end-of-life</t>
-  </si>
-  <si>
-    <t>retired</t>
-  </si>
-  <si>
     <t>information-system-owner-emb</t>
   </si>
   <si>
@@ -712,337 +691,364 @@
     <t>NPS Today</t>
   </si>
   <si>
-    <t>app-1</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
-    <t>app-2</t>
-  </si>
-  <si>
-    <t>app-3</t>
-  </si>
-  <si>
-    <t>app-4</t>
-  </si>
-  <si>
-    <t>app-5</t>
-  </si>
-  <si>
-    <t>app-6</t>
-  </si>
-  <si>
-    <t>app-7</t>
-  </si>
-  <si>
-    <t>app-8</t>
-  </si>
-  <si>
-    <t>app-9</t>
-  </si>
-  <si>
-    <t>app-10</t>
-  </si>
-  <si>
-    <t>app-11</t>
-  </si>
-  <si>
-    <t>app-12</t>
-  </si>
-  <si>
-    <t>app-13</t>
-  </si>
-  <si>
-    <t>app-14</t>
-  </si>
-  <si>
-    <t>app-15</t>
-  </si>
-  <si>
-    <t>app-16</t>
-  </si>
-  <si>
-    <t>app-17</t>
-  </si>
-  <si>
-    <t>app-18</t>
-  </si>
-  <si>
-    <t>app-19</t>
-  </si>
-  <si>
-    <t>app-20</t>
-  </si>
-  <si>
-    <t>app-21</t>
-  </si>
-  <si>
-    <t>app-22</t>
-  </si>
-  <si>
-    <t>app-23</t>
-  </si>
-  <si>
-    <t>app-24</t>
-  </si>
-  <si>
-    <t>app-25</t>
-  </si>
-  <si>
-    <t>app-26</t>
-  </si>
-  <si>
-    <t>app-27</t>
-  </si>
-  <si>
-    <t>app-28</t>
-  </si>
-  <si>
-    <t>app-29</t>
-  </si>
-  <si>
-    <t>app-30</t>
-  </si>
-  <si>
-    <t>app-31</t>
-  </si>
-  <si>
-    <t>app-32</t>
-  </si>
-  <si>
-    <t>app-33</t>
-  </si>
-  <si>
-    <t>app-34</t>
-  </si>
-  <si>
-    <t>app-35</t>
-  </si>
-  <si>
-    <t>app-36</t>
-  </si>
-  <si>
-    <t>app-37</t>
-  </si>
-  <si>
-    <t>app-38</t>
-  </si>
-  <si>
-    <t>app-39</t>
-  </si>
-  <si>
-    <t>app-40</t>
-  </si>
-  <si>
-    <t>app-41</t>
-  </si>
-  <si>
-    <t>app-42</t>
-  </si>
-  <si>
-    <t>app-43</t>
-  </si>
-  <si>
-    <t>app-44</t>
-  </si>
-  <si>
-    <t>app-45</t>
-  </si>
-  <si>
-    <t>app-46</t>
-  </si>
-  <si>
-    <t>app-47</t>
-  </si>
-  <si>
-    <t>app-48</t>
-  </si>
-  <si>
-    <t>app-49</t>
-  </si>
-  <si>
-    <t>app-50</t>
-  </si>
-  <si>
-    <t>app-51</t>
-  </si>
-  <si>
-    <t>app-52</t>
-  </si>
-  <si>
-    <t>app-53</t>
-  </si>
-  <si>
-    <t>app-54</t>
-  </si>
-  <si>
-    <t>app-55</t>
-  </si>
-  <si>
-    <t>app-56</t>
-  </si>
-  <si>
-    <t>app-57</t>
-  </si>
-  <si>
-    <t>app-58</t>
-  </si>
-  <si>
-    <t>app-59</t>
-  </si>
-  <si>
-    <t>app-60</t>
-  </si>
-  <si>
-    <t>app-61</t>
-  </si>
-  <si>
-    <t>app-62</t>
-  </si>
-  <si>
-    <t>app-63</t>
-  </si>
-  <si>
-    <t>app-64</t>
-  </si>
-  <si>
-    <t>app-65</t>
-  </si>
-  <si>
-    <t>app-66</t>
-  </si>
-  <si>
-    <t>app-67</t>
-  </si>
-  <si>
-    <t>app-68</t>
-  </si>
-  <si>
-    <t>app-69</t>
-  </si>
-  <si>
-    <t>app-70</t>
-  </si>
-  <si>
-    <t>app-71</t>
-  </si>
-  <si>
-    <t>app-72</t>
-  </si>
-  <si>
-    <t>app-73</t>
-  </si>
-  <si>
-    <t>app-74</t>
-  </si>
-  <si>
-    <t>app-75</t>
-  </si>
-  <si>
-    <t>app-76</t>
-  </si>
-  <si>
-    <t>app-77</t>
-  </si>
-  <si>
-    <t>app-78</t>
-  </si>
-  <si>
-    <t>app-79</t>
-  </si>
-  <si>
-    <t>app-80</t>
-  </si>
-  <si>
-    <t>app-81</t>
-  </si>
-  <si>
-    <t>app-82</t>
-  </si>
-  <si>
-    <t>app-83</t>
-  </si>
-  <si>
-    <t>app-84</t>
-  </si>
-  <si>
-    <t>app-85</t>
-  </si>
-  <si>
-    <t>app-86</t>
-  </si>
-  <si>
-    <t>app-87</t>
-  </si>
-  <si>
-    <t>app-88</t>
-  </si>
-  <si>
-    <t>app-89</t>
-  </si>
-  <si>
-    <t>app-90</t>
-  </si>
-  <si>
-    <t>app-91</t>
-  </si>
-  <si>
-    <t>app-92</t>
-  </si>
-  <si>
-    <t>app-93</t>
-  </si>
-  <si>
-    <t>app-94</t>
-  </si>
-  <si>
-    <t>app-95</t>
-  </si>
-  <si>
-    <t>app-96</t>
-  </si>
-  <si>
-    <t>app-97</t>
-  </si>
-  <si>
-    <t>app-98</t>
-  </si>
-  <si>
-    <t>app-99</t>
-  </si>
-  <si>
-    <t>app-100</t>
-  </si>
-  <si>
-    <t>app-101</t>
-  </si>
-  <si>
-    <t>app-102</t>
-  </si>
-  <si>
-    <t>app-103</t>
-  </si>
-  <si>
-    <t>app-104</t>
-  </si>
-  <si>
-    <t>app-105</t>
-  </si>
-  <si>
-    <t>app-106</t>
-  </si>
-  <si>
-    <t>app-107</t>
-  </si>
-  <si>
     <t>Department</t>
   </si>
   <si>
-    <t>Application</t>
-  </si>
-  <si>
-    <t>Name</t>
+    <t>Identity‑management and automation platform for Active Directory, Entra ID, Exchange, and Microsoft 365.</t>
+  </si>
+  <si>
+    <t>Supplier of custom‑printed agricultural labels and tags for growers and packers.</t>
+  </si>
+  <si>
+    <t>Plant‑breeding and variety‑testing software for trial data management and analysis.</t>
+  </si>
+  <si>
+    <t>Cloud email‑sending service for transactional and marketing emails.</t>
+  </si>
+  <si>
+    <t>Cloud enterprise planning and forecasting platform for financial and operational modeling.</t>
+  </si>
+  <si>
+    <t>Air‑gapped backup solution protecting data from ransomware and enabling secure recovery.</t>
+  </si>
+  <si>
+    <t>Cloud contact‑center telephony platform for inbound/outbound calling and routing.</t>
+  </si>
+  <si>
+    <t>Enterprise label‑design and barcode‑printing software.</t>
+  </si>
+  <si>
+    <t>Professional barcode and label design software for automated printing.</t>
+  </si>
+  <si>
+    <t>Government service portal for business registrations, court services, and property records.</t>
+  </si>
+  <si>
+    <t>Online marketplace featuring emerging golf brands and independent creators.</t>
+  </si>
+  <si>
+    <t>Marketing automation platform integrated with Microsoft Dynamics 365.</t>
+  </si>
+  <si>
+    <t>CIGAM BR</t>
+  </si>
+  <si>
+    <t>Brazilian ERP system for finance, HR, manufacturing, CRM, and logistics.</t>
+  </si>
+  <si>
+    <t>Productivity and project‑management apps for scheduling and task management.</t>
+  </si>
+  <si>
+    <t>Service‑management app for JENSEN industrial equipment.</t>
+  </si>
+  <si>
+    <t>French‑localized version of the JENSEN service and spare‑parts app.</t>
+  </si>
+  <si>
+    <t>Consultant‑support mobile app for sharing materials and managing contacts.</t>
+  </si>
+  <si>
+    <t>Microsoft CRM platform for managing leads, opportunities, and sales forecasting.</t>
+  </si>
+  <si>
+    <t>Danish manufacturer of industrial weighing and dosing systems.</t>
+  </si>
+  <si>
+    <t>Tabular data‑warehouse structures for analytics and reporting.</t>
+  </si>
+  <si>
+    <t>Tools and processes for retiring legacy systems while preserving data.</t>
+  </si>
+  <si>
+    <t>Strategic retirement of outdated applications and infrastructure.</t>
+  </si>
+  <si>
+    <t>E‑commerce platform for Deer Creek Outdoor Gear.</t>
+  </si>
+  <si>
+    <t>Practices and tools integrating development and IT operations for automated delivery.</t>
+  </si>
+  <si>
+    <t>Real‑estate development and project‑management operations under DLF.</t>
+  </si>
+  <si>
+    <t>Systems for storing, tracking, and retrieving digital documents.</t>
+  </si>
+  <si>
+    <t>Digital‑signature and workflow automation for HR processes.</t>
+  </si>
+  <si>
+    <t>Internal DP World production‑management portal.</t>
+  </si>
+  <si>
+    <t>DP World’s internal employee portal for documentation and workflows.</t>
+  </si>
+  <si>
+    <t>Enterprise search engine for indexing and querying large document sets.</t>
+  </si>
+  <si>
+    <t>eCommerce, CMS, and PIM platform integrated with Microsoft Dynamics.</t>
+  </si>
+  <si>
+    <t>Document‑management automation for QA workflows.</t>
+  </si>
+  <si>
+    <t>Permission and security‑management add‑on for Microsoft Dynamics NAV/BC.</t>
+  </si>
+  <si>
+    <t>EXIMIA</t>
+  </si>
+  <si>
+    <t>Brazilian ERP and business‑management platform.</t>
+  </si>
+  <si>
+    <t>Databases providing import/export records and logistics intelligence.</t>
+  </si>
+  <si>
+    <t>Digital agronomy platform for crop scouting, soil sampling, and field analytics.</t>
+  </si>
+  <si>
+    <t>HRIS platform for recruitment, onboarding, and employee management.</t>
+  </si>
+  <si>
+    <t>Dynamic instrumentation toolkit for inspecting and modifying running applications.</t>
+  </si>
+  <si>
+    <t>QR‑based attendance‑tracking mobile app.</t>
+  </si>
+  <si>
+    <t>Statistical analysis software widely used in agriculture and biology.</t>
+  </si>
+  <si>
+    <t>HR and payroll management platform used in Uruguay.</t>
+  </si>
+  <si>
+    <t>Google Earth Pro</t>
+  </si>
+  <si>
+    <t>Desktop geospatial visualization tool for satellite imagery and GIS data.</t>
+  </si>
+  <si>
+    <t>Unified communications suite with VoIP, messaging, and video conferencing.</t>
+  </si>
+  <si>
+    <t>Platforms providing grain‑market pricing, bids, and trading data.</t>
+  </si>
+  <si>
+    <t>Grower portal for accessing farm maps, harvest data, and documents.</t>
+  </si>
+  <si>
+    <t>Online salon‑booking platforms for scheduling appointments.</t>
+  </si>
+  <si>
+    <t>Cloud vulnerability‑scanning platform for websites, APIs, and servers.</t>
+  </si>
+  <si>
+    <t>SCADA system for industrial automation monitoring and control.</t>
+  </si>
+  <si>
+    <t>JDE</t>
+  </si>
+  <si>
+    <t>Enterprise resource planning system (JD Edwards).</t>
+  </si>
+  <si>
+    <t>Excel‑based reporting tool for Microsoft Dynamics ERP.</t>
+  </si>
+  <si>
+    <t>Issue‑tracking and project‑management platform for agile development.</t>
+  </si>
+  <si>
+    <t>Open‑source password manager storing encrypted credentials locally.</t>
+  </si>
+  <si>
+    <t>EDI solution integrated with Microsoft Dynamics 365 Business Central.</t>
+  </si>
+  <si>
+    <t>Lease‑management and accounting software supporting IFRS/ASC standards.</t>
+  </si>
+  <si>
+    <t>Collaborative email and application platform.</t>
+  </si>
+  <si>
+    <t>Cloud productivity suite including Office apps, Teams, and OneDrive.</t>
+  </si>
+  <si>
+    <t>Madcap</t>
+  </si>
+  <si>
+    <t>Technical documentation and content‑authoring software.</t>
+  </si>
+  <si>
+    <t>Numeric computing platform for modeling, simulation, and data analysis.</t>
+  </si>
+  <si>
+    <t>Enterprise mobility‑management platform for securing and managing devices.</t>
+  </si>
+  <si>
+    <t>Customer portal for accessing seed‑related data and documents.</t>
+  </si>
+  <si>
+    <t>Distribution‑focused version of the MyDLF portal.</t>
+  </si>
+  <si>
+    <t>Wholesale‑oriented MyDLF portal for product and pricing access.</t>
+  </si>
+  <si>
+    <t>Cloud accounting and business‑management platform.</t>
+  </si>
+  <si>
+    <t>Payroll and workforce‑management system for medium/large businesses.</t>
+  </si>
+  <si>
+    <t>Management and automation platform for Azure Virtual Desktop.</t>
+  </si>
+  <si>
+    <t>Label‑design and printing software for barcodes and RFID.</t>
+  </si>
+  <si>
+    <t>Placeholder indicating an application without an assigned owner.</t>
+  </si>
+  <si>
+    <t>Nomos</t>
+  </si>
+  <si>
+    <t>Legal or compliance‑related software (varies by region).</t>
+  </si>
+  <si>
+    <t>Net Promoter Score platform for customer‑loyalty measurement.</t>
+  </si>
+  <si>
+    <t>Automated NPS/CSAT/CES survey platform with dashboards.</t>
+  </si>
+  <si>
+    <t>Multidimensional analytical cubes for sales and logistics reporting.</t>
+  </si>
+  <si>
+    <t>UK supplier of agricultural and environmental seed mixtures.</t>
+  </si>
+  <si>
+    <t>Corporate‑performance‑management platform for financial consolidation and planning.</t>
+  </si>
+  <si>
+    <t>Business‑planning and forecasting software.</t>
+  </si>
+  <si>
+    <t>Automated patch‑management tool for Windows and third‑party apps.</t>
+  </si>
+  <si>
+    <t>Cloud HR and payroll platform with workforce‑management tools.</t>
+  </si>
+  <si>
+    <t>Software supporting plant‑breeding workflows and trait tracking.</t>
+  </si>
+  <si>
+    <t>Export‑documentation and compliance software.</t>
+  </si>
+  <si>
+    <t>Internal product‑information database (custom system).</t>
+  </si>
+  <si>
+    <t>Promap</t>
+  </si>
+  <si>
+    <t>Mapping and property‑information platform.</t>
+  </si>
+  <si>
+    <t>PSIG AR</t>
+  </si>
+  <si>
+    <t>Accounts‑receivable and financial‑management software.</t>
+  </si>
+  <si>
+    <t>SAP Quality Issue Resolution tools for customer complaints.</t>
+  </si>
+  <si>
+    <t>QuickBooks point‑of‑sale system for retail operations.</t>
+  </si>
+  <si>
+    <t>General reference to research‑and‑development listings.</t>
+  </si>
+  <si>
+    <t>Cloud RADIUS authentication service with certificate‑based access.</t>
+  </si>
+  <si>
+    <t>Region‑specific corporate or service websites.</t>
+  </si>
+  <si>
+    <t>Royalty payment calc</t>
+  </si>
+  <si>
+    <t>Tools for calculating royalty payments.</t>
+  </si>
+  <si>
+    <t>Health‑and‑safety management system for incident and risk tracking.</t>
+  </si>
+  <si>
+    <t>Systems for collecting participant or sample data.</t>
+  </si>
+  <si>
+    <t>Cloud HCM suite for HR, payroll, and workforce analytics.</t>
+  </si>
+  <si>
+    <t>European e‑signature and digital‑identity platform.</t>
+  </si>
+  <si>
+    <t>Seed‑science research platforms.</t>
+  </si>
+  <si>
+    <t>Autonomous robotic system for planting seeds.</t>
+  </si>
+  <si>
+    <t>Online seed‑retail platforms for growers and consumers.</t>
+  </si>
+  <si>
+    <t>Transportation‑management system for shipment tracking and routing.</t>
+  </si>
+  <si>
+    <t>Uruguay‑based electronic‑invoicing software.</t>
+  </si>
+  <si>
+    <t>Time‑tracking and attendance‑management system.</t>
+  </si>
+  <si>
+    <t>SQL Spreads</t>
+  </si>
+  <si>
+    <t>Excel‑based data‑management tool for SQL Server.</t>
+  </si>
+  <si>
+    <t>No known enterprise software; unrelated public references.</t>
+  </si>
+  <si>
+    <t>Remote‑access and remote‑support platform.</t>
+  </si>
+  <si>
+    <t>Open‑source machine‑learning framework.</t>
+  </si>
+  <si>
+    <t>Low‑code data‑integration and data‑warehouse automation platform.</t>
+  </si>
+  <si>
+    <t>IT service‑management and enterprise‑service‑management platform.</t>
+  </si>
+  <si>
+    <t>Hardware/software solutions for construction, agriculture, and geospatial mapping.</t>
+  </si>
+  <si>
+    <t>EDI and supply‑chain‑integration platform.</t>
+  </si>
+  <si>
+    <t>No enterprise software identified under this name.</t>
+  </si>
+  <si>
+    <t>Cloud accounting platform for small businesses.</t>
+  </si>
+  <si>
+    <t>Apps for tracking crop yields and field performance.</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1385,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1793,6 +1799,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1838,7 +1868,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1957,6 +1987,28 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2002,10 +2054,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -2048,43 +2097,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2094,9 +2106,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2364,35 +2373,30 @@
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="2" xr16:uid="{C6B7A9E7-CC90-4128-BBB1-5E98C5EC7D88}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="6">
-    <queryTableFields count="5">
+    <queryTableFields count="4">
       <queryTableField id="1" name="Index" tableColumnId="1"/>
-      <queryTableField id="2" name="Custom" tableColumnId="2"/>
       <queryTableField id="3" name="Value" tableColumnId="3"/>
       <queryTableField id="4" name="Region" tableColumnId="4"/>
       <queryTableField id="5" name="Attribute" tableColumnId="5"/>
     </queryTableFields>
+    <queryTableDeletedFields count="1">
+      <deletedField name="Custom"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="3" xr16:uid="{0BF35626-0056-4BB2-BEDC-4CD3A981294A}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="32">
-    <queryTableFields count="31">
-      <queryTableField id="1" name="name" tableColumnId="1"/>
+  <queryTableRefresh nextId="33">
+    <queryTableFields count="24">
+      <queryTableField id="3" name="application" tableColumnId="3"/>
       <queryTableField id="2" name="specification" tableColumnId="2"/>
-      <queryTableField id="3" name="application" tableColumnId="3"/>
-      <queryTableField id="4" name="strategic-business-unit-sbu" tableColumnId="4"/>
       <queryTableField id="5" name="country" tableColumnId="5"/>
       <queryTableField id="6" name="city" tableColumnId="6"/>
-      <queryTableField id="7" name="address" tableColumnId="7"/>
       <queryTableField id="8" name="brief-description" tableColumnId="8"/>
       <queryTableField id="9" name="purpose" tableColumnId="9"/>
       <queryTableField id="10" name="compliance-status" tableColumnId="10"/>
-      <queryTableField id="11" name="developed" tableColumnId="11"/>
-      <queryTableField id="12" name="in-prod" tableColumnId="12"/>
-      <queryTableField id="13" name="end-of-life" tableColumnId="13"/>
-      <queryTableField id="14" name="retired" tableColumnId="14"/>
       <queryTableField id="15" name="information-system-owner-emb" tableColumnId="15"/>
       <queryTableField id="16" name="business-requirement-owner-elt" tableColumnId="16"/>
       <queryTableField id="17" name="business-owner" tableColumnId="17"/>
@@ -2411,61 +2415,62 @@
       <queryTableField id="30" name="backup-1" tableColumnId="30"/>
       <queryTableField id="31" name="environment-1" tableColumnId="31"/>
     </queryTableFields>
+    <queryTableDeletedFields count="7">
+      <deletedField name="name"/>
+      <deletedField name="strategic-business-unit-sbu"/>
+      <deletedField name="address"/>
+      <deletedField name="developed"/>
+      <deletedField name="in-prod"/>
+      <deletedField name="end-of-life"/>
+      <deletedField name="retired"/>
+    </queryTableDeletedFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02302560-6EED-4639-90D1-273165198CCB}" name="Table1" displayName="Table1" ref="A1:J6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" tableBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02302560-6EED-4639-90D1-273165198CCB}" name="Table1" displayName="Table1" ref="A1:J6" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
   <autoFilter ref="A1:J6" xr:uid="{02302560-6EED-4639-90D1-273165198CCB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C667E8BD-FED1-4583-8144-49880E94E97E}" name="Region" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{60C04073-633F-497A-805F-ABC85A176667}" name="Production\Ops" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{9EE4AD61-E9D8-4137-9E0A-62D09727E82F}" name="Supply Chain and Cust Service" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{7AEA7255-B59E-4FD9-95BE-909AFA95566B}" name="Grower Services" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{9A5E54AE-C6C6-4473-A9C1-88DC666ACE92}" name="Sales" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{D1A40079-A931-40F2-8D70-6BBB225036E3}" name="Marketing Product Mgmt" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{0CB245B6-AD23-4851-9DE2-BB347FD351B2}" name="Finance" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{7A95D29E-1EDD-4E9D-AE3D-2C07E1116511}" name="IT" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{70D80CFD-FE11-4C4D-A48B-719ACFC7B53F}" name="HR" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{5DB6B063-B9AA-4BCC-A536-585AB9E17917}" name="R&amp;D" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{C667E8BD-FED1-4583-8144-49880E94E97E}" name="Region" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{60C04073-633F-497A-805F-ABC85A176667}" name="Production\Ops" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{9EE4AD61-E9D8-4137-9E0A-62D09727E82F}" name="Supply Chain and Cust Service" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{7AEA7255-B59E-4FD9-95BE-909AFA95566B}" name="Grower Services" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{9A5E54AE-C6C6-4473-A9C1-88DC666ACE92}" name="Sales" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{D1A40079-A931-40F2-8D70-6BBB225036E3}" name="Marketing Product Mgmt" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{0CB245B6-AD23-4851-9DE2-BB347FD351B2}" name="Finance" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{7A95D29E-1EDD-4E9D-AE3D-2C07E1116511}" name="IT" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{70D80CFD-FE11-4C4D-A48B-719ACFC7B53F}" name="HR" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{5DB6B063-B9AA-4BCC-A536-585AB9E17917}" name="R&amp;D" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E0C9DBB6-6145-4DCD-9FA0-6D82D0B76BEB}" name="Table1_2" displayName="Table1_2" ref="A1:E108" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:E108" xr:uid="{E0C9DBB6-6145-4DCD-9FA0-6D82D0B76BEB}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5BFFD9C2-5D7C-4A12-94FA-5C3F04F53C6C}" uniqueName="1" name="Index" queryTableFieldId="1" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{EA170144-8290-4FB8-8E04-266141DE0E2C}" uniqueName="2" name="Name" queryTableFieldId="2" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{1AC0E3CA-EDCE-4BE9-81B5-B0A710CF6535}" uniqueName="3" name="Application" queryTableFieldId="3" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{155595B7-8BE5-4F11-B27C-AD1B448DCEAA}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{78E264CD-3C7B-4A7A-903A-30806ADFDC7D}" uniqueName="5" name="Department" queryTableFieldId="5" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E0C9DBB6-6145-4DCD-9FA0-6D82D0B76BEB}" name="Table1_2" displayName="Table1_2" ref="A1:D124" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:D124" xr:uid="{E0C9DBB6-6145-4DCD-9FA0-6D82D0B76BEB}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{5BFFD9C2-5D7C-4A12-94FA-5C3F04F53C6C}" uniqueName="1" name="Index" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{1AC0E3CA-EDCE-4BE9-81B5-B0A710CF6535}" uniqueName="3" name="name" queryTableFieldId="3" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{155595B7-8BE5-4F11-B27C-AD1B448DCEAA}" uniqueName="4" name="Region" queryTableFieldId="4" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{78E264CD-3C7B-4A7A-903A-30806ADFDC7D}" uniqueName="5" name="Department" queryTableFieldId="5" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5AA0A5C2-4B07-40B3-907E-4A2528BF12F5}" name="Table12" displayName="Table12" ref="A1:AE108" totalsRowShown="0">
-  <autoFilter ref="A1:AE108" xr:uid="{5AA0A5C2-4B07-40B3-907E-4A2528BF12F5}"/>
-  <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{A5EAADD4-C1E8-49E2-AA09-CEF70C8C181B}" name="name" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5AA0A5C2-4B07-40B3-907E-4A2528BF12F5}" name="Table12" displayName="Table12" ref="A1:X108" totalsRowShown="0">
+  <autoFilter ref="A1:X108" xr:uid="{5AA0A5C2-4B07-40B3-907E-4A2528BF12F5}"/>
+  <tableColumns count="24">
+    <tableColumn id="3" xr3:uid="{E98E198B-F738-450C-8375-6574E4784EE5}" name="name" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{46D5AB6B-CD54-4E67-BC5B-C3658B4C9923}" name="specification"/>
-    <tableColumn id="3" xr3:uid="{E98E198B-F738-450C-8375-6574E4784EE5}" name="application" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{F7FEE9E5-81D3-41C5-B959-8D97A32E575D}" name="strategic-business-unit-sbu"/>
     <tableColumn id="5" xr3:uid="{89785BDD-7BDE-401B-99BF-264A92D41332}" name="country"/>
     <tableColumn id="6" xr3:uid="{034D2C69-4649-45AE-8278-6832C04D4B16}" name="city"/>
-    <tableColumn id="7" xr3:uid="{AFF97A42-3B33-4AAC-8DEF-D1C540B90520}" name="address"/>
     <tableColumn id="8" xr3:uid="{6753901C-1182-4225-9702-53A33C830D93}" name="brief-description"/>
     <tableColumn id="9" xr3:uid="{DC63D878-DF21-4161-9DF6-32E5E8D57157}" name="purpose"/>
     <tableColumn id="10" xr3:uid="{01DED0A8-CBAA-4344-A74B-D125D3249F4D}" name="compliance-status"/>
-    <tableColumn id="11" xr3:uid="{4B8FFC5F-8182-4D5D-9BB3-478BD212FBBD}" name="developed"/>
-    <tableColumn id="12" xr3:uid="{C88343E7-3EDE-4880-8EC1-38A88A833A8D}" name="in-prod"/>
-    <tableColumn id="13" xr3:uid="{63A4C67B-756F-4735-B58C-510DFBE24273}" name="end-of-life"/>
-    <tableColumn id="14" xr3:uid="{46A6C28D-BCD4-4FA4-ACB2-FD6D9F601034}" name="retired"/>
     <tableColumn id="15" xr3:uid="{8E336954-ADD3-4409-9D00-C6DA409CF562}" name="information-system-owner-emb"/>
     <tableColumn id="16" xr3:uid="{58224A53-D86C-45C7-B36C-168E210FF39F}" name="business-requirement-owner-elt"/>
     <tableColumn id="17" xr3:uid="{8A6B844C-EA10-4BE9-BFE7-7EBA2AB233C8}" name="business-owner"/>
@@ -2489,23 +2494,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{90EABF2B-40A1-4021-AAAC-692B3C04AA9C}" name="Table12_1" displayName="Table12_1" ref="A1:AE98" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:AE98" xr:uid="{90EABF2B-40A1-4021-AAAC-692B3C04AA9C}"/>
-  <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{4BE4BE3B-9F91-4F29-80E5-99D515DE2139}" uniqueName="1" name="name" queryTableFieldId="1" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{90EABF2B-40A1-4021-AAAC-692B3C04AA9C}" name="Table12_1" displayName="Table12_1" ref="A1:X110" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:X110" xr:uid="{90EABF2B-40A1-4021-AAAC-692B3C04AA9C}"/>
+  <tableColumns count="24">
+    <tableColumn id="3" xr3:uid="{1CDC4479-8937-484D-9AF2-89E7289EA457}" uniqueName="3" name="name" queryTableFieldId="3" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{44195442-0596-47F5-A60D-BBA4B5C331C8}" uniqueName="2" name="specification" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{1CDC4479-8937-484D-9AF2-89E7289EA457}" uniqueName="3" name="application" queryTableFieldId="3" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{49DEFF02-6AE3-40DE-86B3-97ABDBDDA8E3}" uniqueName="4" name="strategic-business-unit-sbu" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{D4B83A91-F567-4D1B-A31F-742194911134}" uniqueName="5" name="country" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{BF8166C2-0697-4CD5-93B6-3C101456551F}" uniqueName="6" name="city" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{4866E411-1DA4-4246-B723-488138ED9363}" uniqueName="7" name="address" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{9360A238-39B1-4860-8305-3CA42430C716}" uniqueName="8" name="brief-description" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{7AEA292B-9226-47A3-BE90-C6C788BBCE39}" uniqueName="9" name="purpose" queryTableFieldId="9"/>
     <tableColumn id="10" xr3:uid="{9E9691C5-E8A0-427F-82C5-A0415C74D001}" uniqueName="10" name="compliance-status" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{844CD12C-5D1A-45F3-AD2E-0B05C3EA911D}" uniqueName="11" name="developed" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{699DC6A4-ACDE-4265-B6E9-909628C02E0E}" uniqueName="12" name="in-prod" queryTableFieldId="12"/>
-    <tableColumn id="13" xr3:uid="{848CAF47-9877-42FE-872D-E57E19D616ED}" uniqueName="13" name="end-of-life" queryTableFieldId="13"/>
-    <tableColumn id="14" xr3:uid="{D0AC2888-460B-4E77-8747-42D5F20A9806}" uniqueName="14" name="retired" queryTableFieldId="14"/>
     <tableColumn id="15" xr3:uid="{2384739B-01E5-4CAB-BDD9-A8862449D145}" uniqueName="15" name="information-system-owner-emb" queryTableFieldId="15"/>
     <tableColumn id="16" xr3:uid="{492BC159-AC12-42D0-9580-7C4A9B2BD31D}" uniqueName="16" name="business-requirement-owner-elt" queryTableFieldId="16"/>
     <tableColumn id="17" xr3:uid="{5DDC4DA9-C8A0-475C-A33B-2BE4DD33F6E0}" uniqueName="17" name="business-owner" queryTableFieldId="17"/>
@@ -3360,1850 +3358,1750 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C35322-2D49-45A1-9A38-61F1DD60535D}">
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="36" customWidth="1"/>
-    <col min="2" max="2" width="12.25" style="36" customWidth="1"/>
-    <col min="3" max="3" width="26.5" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.375" style="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.75" style="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.75" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>295</v>
+        <v>153</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>294</v>
+        <v>63</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="36" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="36">
         <v>1</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>185</v>
+        <v>54</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="36" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="36">
         <v>2</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="36">
         <v>3</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="36" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="36">
         <v>4</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>5</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="36" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="36">
         <v>6</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>191</v>
+        <v>67</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>7</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="39">
         <v>8</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="39" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>8</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="39" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>8</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="39" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>11</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
         <v>12</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>13</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
         <v>14</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="36" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>15</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>200</v>
+        <v>74</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="36" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
         <v>16</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>201</v>
+        <v>75</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="36" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>17</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="36" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="36">
         <v>18</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>19</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>20</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <v>21</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
         <v>22</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="36" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>23</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="36" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="36">
         <v>24</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>25</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="36">
         <v>26</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>211</v>
+        <v>85</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
         <v>27</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>212</v>
+        <v>86</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="36">
         <v>28</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>213</v>
+        <v>87</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>29</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>214</v>
+        <v>88</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <v>30</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>215</v>
+        <v>89</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="36">
         <v>31</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>216</v>
+        <v>90</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="36">
         <v>32</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>217</v>
+        <v>91</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="36">
         <v>33</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="36">
         <v>34</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>219</v>
+        <v>93</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E35" s="36" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="36">
         <v>35</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>220</v>
+        <v>94</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="36">
         <v>36</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="36">
         <v>37</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E38" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="36">
         <v>38</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>223</v>
+        <v>97</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E39" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="36">
         <v>39</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="36">
         <v>40</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>225</v>
+        <v>98</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="D41" s="36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="39">
+        <v>41</v>
+      </c>
+      <c r="B42" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="36" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="36">
-        <v>41</v>
-      </c>
-      <c r="B42" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="C42" s="36" t="s">
+      <c r="D42" s="39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="39">
+        <v>42</v>
+      </c>
+      <c r="B43" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="D42" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E42" s="36" t="s">
+      <c r="C43" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="39" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="36">
-        <v>42</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="C43" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="36">
         <v>43</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>228</v>
+        <v>100</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" s="36" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="36">
         <v>44</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>229</v>
+        <v>101</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="36">
         <v>45</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>230</v>
+        <v>102</v>
       </c>
       <c r="C46" s="36" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="D46" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="36" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="36">
         <v>46</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>231</v>
+        <v>103</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="36">
         <v>47</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>232</v>
+        <v>104</v>
       </c>
       <c r="C48" s="36" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="36">
         <v>48</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>233</v>
+        <v>105</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>105</v>
+        <v>12</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="36">
         <v>49</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>234</v>
+        <v>106</v>
       </c>
       <c r="C50" s="36" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="D50" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E50" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="36">
         <v>50</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>235</v>
+        <v>107</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="D51" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E51" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="36">
         <v>51</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>236</v>
+        <v>108</v>
       </c>
       <c r="C52" s="36" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="D52" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E52" s="36" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="36">
         <v>52</v>
       </c>
       <c r="B53" s="36" t="s">
-        <v>237</v>
+        <v>109</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="36">
         <v>53</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>238</v>
+        <v>110</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E54" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="36">
         <v>54</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>239</v>
+        <v>152</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>152</v>
+        <v>33</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E55" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="36">
         <v>55</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="C56" s="36" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="D56" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E56" s="36" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="36">
         <v>56</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>241</v>
+        <v>112</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="D57" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E57" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="36">
         <v>57</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="C58" s="36" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="D58" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E58" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="36">
         <v>58</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E59" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="36">
         <v>59</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="C60" s="36" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E60" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="39">
         <v>60</v>
       </c>
       <c r="B61" s="39" t="s">
-        <v>245</v>
+        <v>116</v>
       </c>
       <c r="C61" s="39" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="D61" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E61" s="39" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="39">
         <v>60</v>
       </c>
       <c r="B62" s="39" t="s">
-        <v>245</v>
+        <v>116</v>
       </c>
       <c r="C62" s="39" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="D62" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="E62" s="39" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="39">
         <v>60</v>
       </c>
       <c r="B63" s="39" t="s">
-        <v>245</v>
+        <v>116</v>
       </c>
       <c r="C63" s="39" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="D63" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" s="39" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="36">
         <v>63</v>
       </c>
       <c r="B64" s="36" t="s">
-        <v>248</v>
+        <v>177</v>
       </c>
       <c r="C64" s="36" t="s">
-        <v>184</v>
+        <v>33</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E64" s="36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="36">
         <v>64</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>249</v>
+        <v>117</v>
       </c>
       <c r="C65" s="36" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="D65" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="39">
         <v>65</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="C66" s="39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D66" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="39" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="39">
         <v>65</v>
       </c>
       <c r="B67" s="39" t="s">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="C67" s="39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D67" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="39" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="36">
         <v>67</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>252</v>
+        <v>118</v>
       </c>
       <c r="C68" s="36" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E68" s="36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="36">
         <v>68</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>253</v>
+        <v>119</v>
       </c>
       <c r="C69" s="36" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="D69" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E69" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="36">
         <v>69</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>254</v>
+        <v>120</v>
       </c>
       <c r="C70" s="36" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="D70" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E70" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="36">
         <v>70</v>
       </c>
       <c r="B71" s="36" t="s">
-        <v>255</v>
+        <v>121</v>
       </c>
       <c r="C71" s="36" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="D71" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="36">
         <v>71</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>256</v>
+        <v>122</v>
       </c>
       <c r="C72" s="36" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="D72" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E72" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="36">
         <v>72</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>257</v>
+        <v>123</v>
       </c>
       <c r="C73" s="36" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E73" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="36">
         <v>73</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>258</v>
+        <v>124</v>
       </c>
       <c r="C74" s="36" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E74" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="36">
         <v>74</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>259</v>
+        <v>125</v>
       </c>
       <c r="C75" s="36" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="D75" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E75" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="36">
         <v>75</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>260</v>
+        <v>126</v>
       </c>
       <c r="C76" s="36" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E76" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="36">
         <v>76</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>261</v>
+        <v>127</v>
       </c>
       <c r="C77" s="36" t="s">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="D77" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E77" s="36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="36">
         <v>77</v>
       </c>
       <c r="B78" s="36" t="s">
-        <v>262</v>
+        <v>128</v>
       </c>
       <c r="C78" s="36" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="D78" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E78" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="36">
         <v>78</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>263</v>
+        <v>129</v>
       </c>
       <c r="C79" s="36" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="D79" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E79" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="36">
         <v>79</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>264</v>
+        <v>130</v>
       </c>
       <c r="C80" s="36" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="D80" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E80" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="36">
         <v>80</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>265</v>
+        <v>131</v>
       </c>
       <c r="C81" s="36" t="s">
-        <v>131</v>
+        <v>12</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E81" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="36">
         <v>81</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>266</v>
+        <v>132</v>
       </c>
       <c r="C82" s="36" t="s">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="D82" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E82" s="36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="36">
         <v>82</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>267</v>
+        <v>133</v>
       </c>
       <c r="C83" s="36" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E83" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="36">
         <v>83</v>
       </c>
       <c r="B84" s="36" t="s">
-        <v>268</v>
+        <v>134</v>
       </c>
       <c r="C84" s="36" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="D84" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E84" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="36">
         <v>84</v>
       </c>
       <c r="B85" s="36" t="s">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="C85" s="36" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="D85" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E85" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="36">
         <v>85</v>
       </c>
       <c r="B86" s="36" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E86" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="39">
         <v>86</v>
       </c>
       <c r="B87" s="39" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="C87" s="39" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="E87" s="39" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="39">
         <v>86</v>
       </c>
       <c r="B88" s="39" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="C88" s="39" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="D88" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="E88" s="39" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="39">
         <v>88</v>
       </c>
       <c r="B89" s="39" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="C89" s="39" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="E89" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="39">
         <v>88</v>
       </c>
       <c r="B90" s="39" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="C90" s="39" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="D90" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="E90" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="36">
         <v>90</v>
       </c>
       <c r="B91" s="36" t="s">
-        <v>275</v>
+        <v>139</v>
       </c>
       <c r="C91" s="36" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="D91" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E91" s="36" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="36">
         <v>91</v>
       </c>
       <c r="B92" s="36" t="s">
-        <v>276</v>
+        <v>140</v>
       </c>
       <c r="C92" s="36" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="D92" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E92" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="36">
         <v>92</v>
       </c>
       <c r="B93" s="36" t="s">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="C93" s="36" t="s">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="D93" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E93" s="36" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="36">
         <v>93</v>
       </c>
       <c r="B94" s="36" t="s">
-        <v>278</v>
+        <v>37</v>
       </c>
       <c r="C94" s="36" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D94" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E94" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="36">
         <v>94</v>
       </c>
       <c r="B95" s="36" t="s">
-        <v>279</v>
+        <v>142</v>
       </c>
       <c r="C95" s="36" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="D95" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E95" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="36">
         <v>95</v>
       </c>
       <c r="B96" s="36" t="s">
-        <v>280</v>
+        <v>143</v>
       </c>
       <c r="C96" s="36" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E96" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="36">
         <v>96</v>
       </c>
       <c r="B97" s="36" t="s">
-        <v>281</v>
+        <v>144</v>
       </c>
       <c r="C97" s="36" t="s">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="D97" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E97" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="36">
         <v>97</v>
       </c>
       <c r="B98" s="36" t="s">
-        <v>282</v>
+        <v>145</v>
       </c>
       <c r="C98" s="36" t="s">
-        <v>145</v>
+        <v>42</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E98" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="36">
         <v>98</v>
       </c>
       <c r="B99" s="36" t="s">
-        <v>283</v>
+        <v>146</v>
       </c>
       <c r="C99" s="36" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="D99" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E99" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="36">
         <v>99</v>
       </c>
       <c r="B100" s="36" t="s">
-        <v>284</v>
+        <v>147</v>
       </c>
       <c r="C100" s="36" t="s">
-        <v>147</v>
+        <v>12</v>
       </c>
       <c r="D100" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E100" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="39">
         <v>100</v>
       </c>
       <c r="B101" s="39" t="s">
-        <v>285</v>
+        <v>35</v>
       </c>
       <c r="C101" s="39" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D101" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="E101" s="39" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="39">
         <v>100</v>
       </c>
       <c r="B102" s="39" t="s">
-        <v>285</v>
+        <v>35</v>
       </c>
       <c r="C102" s="39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D102" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="E102" s="39" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="39">
         <v>102</v>
       </c>
       <c r="B103" s="39" t="s">
-        <v>287</v>
+        <v>148</v>
       </c>
       <c r="C103" s="39" t="s">
-        <v>148</v>
+        <v>42</v>
       </c>
       <c r="D103" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="E103" s="39" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="39">
         <v>102</v>
       </c>
       <c r="B104" s="39" t="s">
-        <v>287</v>
+        <v>148</v>
       </c>
       <c r="C104" s="39" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="D104" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="E104" s="39" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="36">
         <v>104</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>289</v>
+        <v>30</v>
       </c>
       <c r="C105" s="36" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D105" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E105" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="36">
         <v>105</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>290</v>
+        <v>149</v>
       </c>
       <c r="C106" s="36" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E106" s="36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="36">
         <v>106</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>291</v>
+        <v>150</v>
       </c>
       <c r="C107" s="36" t="s">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="D107" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E107" s="36" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="36">
         <v>107</v>
       </c>
       <c r="B108" s="36" t="s">
-        <v>292</v>
+        <v>151</v>
       </c>
       <c r="C108" s="36" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="D108" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="39">
+        <v>108</v>
+      </c>
+      <c r="B109" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C109" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D109" s="47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="39">
+        <v>109</v>
+      </c>
+      <c r="B110" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="E108" s="36" t="s">
-        <v>1</v>
+      <c r="D110" s="47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="39">
+        <v>110</v>
+      </c>
+      <c r="B111" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" s="47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="39">
+        <v>111</v>
+      </c>
+      <c r="B112" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" s="47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="36">
+        <v>112</v>
+      </c>
+      <c r="B113" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C113" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D113" s="43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="39">
+        <v>113</v>
+      </c>
+      <c r="B114" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C114" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="D114" s="47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="39">
+        <v>114</v>
+      </c>
+      <c r="B115" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C115" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="D115" s="47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="36">
+        <v>115</v>
+      </c>
+      <c r="B116" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="C116" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D116" s="43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="36">
+        <v>116</v>
+      </c>
+      <c r="B117" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="C117" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D117" s="43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="36">
+        <v>117</v>
+      </c>
+      <c r="B118" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="C118" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D118" s="43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="36">
+        <v>118</v>
+      </c>
+      <c r="B119" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="C119" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D119" s="43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="36">
+        <v>119</v>
+      </c>
+      <c r="B120" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="C120" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D120" s="43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="36">
+        <v>120</v>
+      </c>
+      <c r="B121" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="C121" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D121" s="43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="36">
+        <v>121</v>
+      </c>
+      <c r="B122" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="C122" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="D122" s="43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="36">
+        <v>122</v>
+      </c>
+      <c r="B123" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="C123" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D123" s="43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="44">
+        <v>123</v>
+      </c>
+      <c r="B124" s="45" t="s">
+        <v>286</v>
+      </c>
+      <c r="C124" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D124" s="43" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5216,37 +5114,33 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D70948A-D7F6-4CB4-BC49-8EE7DF89CBB8}">
-  <dimension ref="A1:AE108"/>
+  <dimension ref="A1:X108"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.375" customWidth="1"/>
-    <col min="3" max="3" width="26.25" customWidth="1"/>
-    <col min="4" max="4" width="24.875" customWidth="1"/>
-    <col min="7" max="7" width="9.125" customWidth="1"/>
-    <col min="8" max="8" width="16.25" customWidth="1"/>
-    <col min="9" max="9" width="9.25" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="11.125" customWidth="1"/>
-    <col min="13" max="13" width="11.25" customWidth="1"/>
-    <col min="15" max="15" width="28.625" customWidth="1"/>
-    <col min="16" max="16" width="28.875" customWidth="1"/>
-    <col min="17" max="17" width="15.5" customWidth="1"/>
-    <col min="18" max="18" width="9.5" customWidth="1"/>
-    <col min="19" max="19" width="11.625" customWidth="1"/>
-    <col min="21" max="21" width="15.5" customWidth="1"/>
-    <col min="23" max="23" width="15" customWidth="1"/>
-    <col min="24" max="24" width="12.875" customWidth="1"/>
-    <col min="25" max="25" width="14.75" customWidth="1"/>
-    <col min="26" max="26" width="31.125" customWidth="1"/>
-    <col min="27" max="27" width="14.375" customWidth="1"/>
-    <col min="28" max="28" width="18.625" customWidth="1"/>
-    <col min="29" max="29" width="9.375" customWidth="1"/>
-    <col min="30" max="30" width="10.375" customWidth="1"/>
-    <col min="31" max="31" width="14.625" customWidth="1"/>
-    <col min="32" max="32" width="12.25" customWidth="1"/>
+    <col min="1" max="1" width="28.25" customWidth="1"/>
+    <col min="2" max="2" width="26.25" customWidth="1"/>
+    <col min="5" max="5" width="16.25" customWidth="1"/>
+    <col min="6" max="6" width="9.25" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="28.625" customWidth="1"/>
+    <col min="9" max="9" width="28.875" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="9.5" customWidth="1"/>
+    <col min="12" max="12" width="11.625" customWidth="1"/>
+    <col min="14" max="14" width="15.5" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="12.875" customWidth="1"/>
+    <col min="18" max="18" width="14.75" customWidth="1"/>
+    <col min="19" max="19" width="31.125" customWidth="1"/>
+    <col min="20" max="20" width="14.375" customWidth="1"/>
+    <col min="21" max="21" width="18.625" customWidth="1"/>
+    <col min="22" max="22" width="9.375" customWidth="1"/>
+    <col min="23" max="23" width="10.375" customWidth="1"/>
+    <col min="24" max="24" width="14.625" customWidth="1"/>
+    <col min="25" max="25" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>153</v>
       </c>
@@ -5319,881 +5213,539 @@
       <c r="X1" t="s">
         <v>176</v>
       </c>
-      <c r="Y1" t="s">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="37" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="37" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="38" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="37" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="38" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="38" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="38" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="37" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="38" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="37" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="38" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="38" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="37" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="38" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="37" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="Z1" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>181</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>182</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="C22" s="37" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="C24" s="37" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C26" s="37" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="C36" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="C38" s="37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="C39" s="38" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="C40" s="37" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="C41" s="38" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="C44" s="37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="C46" s="37" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="C47" s="38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="C48" s="37" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="C49" s="38" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="C50" s="37" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="C51" s="38" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="C52" s="37" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="C53" s="38" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="C54" s="37" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="C55" s="38" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="37" t="s">
-        <v>240</v>
-      </c>
-      <c r="C56" s="37" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="C57" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="C58" s="37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="37" t="s">
-        <v>244</v>
-      </c>
-      <c r="C60" s="37" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="C61" s="38" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="C62" s="37" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="C63" s="38" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="C64" s="37" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="C65" s="38" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="C66" s="37" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="C67" s="38" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="C68" s="37" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="C69" s="38" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="C70" s="37" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="C71" s="38" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="C72" s="37" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="C73" s="38" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="C74" s="37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="C75" s="38" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="C76" s="37" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="C77" s="38" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="C78" s="37" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="C79" s="38" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="C80" s="37" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="C81" s="38" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="C82" s="37" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="C83" s="38" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="C84" s="37" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="38" t="s">
-        <v>269</v>
-      </c>
-      <c r="C85" s="38" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="C86" s="37" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="C87" s="38" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="C88" s="37" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="38" t="s">
-        <v>273</v>
-      </c>
-      <c r="C89" s="38" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="C90" s="37" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="C91" s="38" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="C92" s="37" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="C93" s="38" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="C94" s="37" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="C95" s="38" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="C96" s="37" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="38" t="s">
-        <v>281</v>
-      </c>
-      <c r="C97" s="38" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="C98" s="37" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="C99" s="38" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="C100" s="37" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="C101" s="38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="C102" s="37" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="C103" s="38" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="C104" s="37" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="C105" s="38" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="C106" s="37" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="38" t="s">
-        <v>291</v>
-      </c>
-      <c r="C107" s="38" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="C108" s="37" t="s">
         <v>151</v>
       </c>
     </row>
@@ -6207,42 +5759,35 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8711472-CC0F-4349-B4D9-92ECD6B661ED}">
-  <dimension ref="A1:AE98"/>
+  <dimension ref="A1:X110"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="31.875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.375" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="4" max="4" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.75" customWidth="1"/>
+    <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>153</v>
       </c>
@@ -6315,802 +5860,874 @@
       <c r="X1" t="s">
         <v>176</v>
       </c>
-      <c r="Y1" t="s">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="E35" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>101</v>
+      </c>
+      <c r="E42" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>104</v>
+      </c>
+      <c r="E45" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>105</v>
+      </c>
+      <c r="E46" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>106</v>
+      </c>
+      <c r="E47" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>107</v>
+      </c>
+      <c r="E48" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>108</v>
+      </c>
+      <c r="E49" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>109</v>
+      </c>
+      <c r="E50" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="E51" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>111</v>
+      </c>
+      <c r="E53" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>112</v>
+      </c>
+      <c r="E54" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>116</v>
+      </c>
+      <c r="E58" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>177</v>
       </c>
-      <c r="Z1" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>181</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>182</v>
-      </c>
-      <c r="AE1" t="s">
+      <c r="E59" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>117</v>
+      </c>
+      <c r="E60" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>118</v>
+      </c>
+      <c r="E62" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>119</v>
+      </c>
+      <c r="E63" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>120</v>
+      </c>
+      <c r="E64" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>121</v>
+      </c>
+      <c r="E65" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>122</v>
+      </c>
+      <c r="E66" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>123</v>
+      </c>
+      <c r="E67" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>126</v>
+      </c>
+      <c r="E70" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>127</v>
+      </c>
+      <c r="E71" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>128</v>
+      </c>
+      <c r="E72" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>129</v>
+      </c>
+      <c r="E73" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>130</v>
+      </c>
+      <c r="E74" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E75" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>132</v>
+      </c>
+      <c r="E76" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>133</v>
+      </c>
+      <c r="E77" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>135</v>
+      </c>
+      <c r="E79" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>136</v>
+      </c>
+      <c r="E80" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>137</v>
+      </c>
+      <c r="E81" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>138</v>
+      </c>
+      <c r="E82" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>139</v>
+      </c>
+      <c r="E83" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>140</v>
+      </c>
+      <c r="E84" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>141</v>
+      </c>
+      <c r="E85" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>37</v>
+      </c>
+      <c r="E86" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>142</v>
+      </c>
+      <c r="E87" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>143</v>
+      </c>
+      <c r="E88" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>144</v>
+      </c>
+      <c r="E89" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>145</v>
+      </c>
+      <c r="E90" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>146</v>
+      </c>
+      <c r="E91" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>147</v>
+      </c>
+      <c r="E92" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>148</v>
+      </c>
+      <c r="E94" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>30</v>
+      </c>
+      <c r="E95" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>149</v>
+      </c>
+      <c r="E96" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>150</v>
+      </c>
+      <c r="E97" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>151</v>
+      </c>
+      <c r="E98" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E99" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="C8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="E100" t="s">
         <v>193</v>
       </c>
-      <c r="C9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>197</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>200</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>201</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>202</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>203</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>205</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>206</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>207</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>209</v>
-      </c>
-      <c r="C23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>210</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>211</v>
-      </c>
-      <c r="C25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>212</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E101" t="s">
         <v>213</v>
       </c>
-      <c r="C27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="E102" t="s">
         <v>215</v>
       </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>216</v>
-      </c>
-      <c r="C30" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>217</v>
-      </c>
-      <c r="C31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>218</v>
-      </c>
-      <c r="C32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>219</v>
-      </c>
-      <c r="C33" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>220</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>221</v>
-      </c>
-      <c r="C35" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>222</v>
-      </c>
-      <c r="C36" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="C37" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="E103" t="s">
         <v>224</v>
       </c>
-      <c r="C38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>225</v>
-      </c>
-      <c r="C39" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>226</v>
-      </c>
-      <c r="C40" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>228</v>
-      </c>
-      <c r="C41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>229</v>
-      </c>
-      <c r="C42" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>230</v>
-      </c>
-      <c r="C43" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="40" t="s">
         <v>231</v>
       </c>
-      <c r="C44" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="E104" t="s">
         <v>232</v>
       </c>
-      <c r="C45" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>233</v>
-      </c>
-      <c r="C46" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>234</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>235</v>
-      </c>
-      <c r="C48" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>236</v>
-      </c>
-      <c r="C49" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>237</v>
-      </c>
-      <c r="C50" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>238</v>
-      </c>
-      <c r="C51" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>239</v>
-      </c>
-      <c r="C52" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="C53" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="E105" t="s">
         <v>241</v>
       </c>
-      <c r="C54" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>242</v>
-      </c>
-      <c r="C55" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>244</v>
-      </c>
-      <c r="C57" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>245</v>
-      </c>
-      <c r="C58" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>248</v>
-      </c>
-      <c r="C59" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>249</v>
-      </c>
-      <c r="C60" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>250</v>
-      </c>
-      <c r="C61" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="40" t="s">
         <v>252</v>
       </c>
-      <c r="C62" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="E106" t="s">
         <v>253</v>
       </c>
-      <c r="C63" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>254</v>
-      </c>
-      <c r="C64" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>255</v>
-      </c>
-      <c r="C65" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>256</v>
-      </c>
-      <c r="C66" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>257</v>
-      </c>
-      <c r="C67" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>258</v>
-      </c>
-      <c r="C68" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>259</v>
-      </c>
-      <c r="C69" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>260</v>
-      </c>
-      <c r="C70" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>261</v>
-      </c>
-      <c r="C71" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>262</v>
-      </c>
-      <c r="C72" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>263</v>
-      </c>
-      <c r="C73" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>264</v>
-      </c>
-      <c r="C74" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="40" t="s">
         <v>265</v>
       </c>
-      <c r="C75" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="E107" t="s">
         <v>266</v>
       </c>
-      <c r="C76" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="40" t="s">
         <v>267</v>
       </c>
-      <c r="C77" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="E108" t="s">
         <v>268</v>
       </c>
-      <c r="C78" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>269</v>
-      </c>
-      <c r="C79" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>270</v>
-      </c>
-      <c r="C80" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>271</v>
-      </c>
-      <c r="C81" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>273</v>
-      </c>
-      <c r="C82" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="E109" t="s">
         <v>275</v>
       </c>
-      <c r="C83" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>276</v>
-      </c>
-      <c r="C84" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>277</v>
-      </c>
-      <c r="C85" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>278</v>
-      </c>
-      <c r="C86" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>279</v>
-      </c>
-      <c r="C87" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>280</v>
-      </c>
-      <c r="C88" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>281</v>
-      </c>
-      <c r="C89" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>282</v>
-      </c>
-      <c r="C90" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>283</v>
-      </c>
-      <c r="C91" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>284</v>
-      </c>
-      <c r="C92" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>285</v>
-      </c>
-      <c r="C93" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="E110" t="s">
         <v>287</v>
-      </c>
-      <c r="C94" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>289</v>
-      </c>
-      <c r="C95" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>290</v>
-      </c>
-      <c r="C96" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>291</v>
-      </c>
-      <c r="C97" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>292</v>
-      </c>
-      <c r="C98" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
